--- a/reference_keys/KEY_Video_4.xlsx
+++ b/reference_keys/KEY_Video_4.xlsx
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Listing is present: 3+ symbols of same part of speech</t>
+          <t>Listing is Not Present</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Listing is present: 3+ symbols of same part of speech</t>
+          <t>Listing is Not Present</t>
         </is>
       </c>
     </row>

--- a/reference_keys/KEY_Video_4.xlsx
+++ b/reference_keys/KEY_Video_4.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t xml:space="preserve">YELLOW DUCK </t>
+          <t>YELLOW DUCK</t>
         </is>
       </c>
     </row>
